--- a/doc/潘多拉STM32L4开发板IO引脚分配表.xlsx
+++ b/doc/潘多拉STM32L4开发板IO引脚分配表.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="21029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23001"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281BF72E-3DA9-43E7-BE2E-6D08E58367A0}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97ECA99-32C2-4FA5-94CC-06AA44AE03ED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
